--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/112.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/112.xlsx
@@ -426,13 +426,13 @@
         <v>-21.95173904396404</v>
       </c>
       <c r="E2">
-        <v>-20.35424348355823</v>
+        <v>-19.41433022863628</v>
       </c>
       <c r="F2">
-        <v>-1.230749501059082</v>
+        <v>-1.61112255854617</v>
       </c>
       <c r="G2">
-        <v>-18.0680712016481</v>
+        <v>-19.38002779506353</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-21.80037838121608</v>
       </c>
       <c r="E3">
-        <v>-20.68363052051906</v>
+        <v>-19.86015254508868</v>
       </c>
       <c r="F3">
-        <v>-2.558528842230173</v>
+        <v>-1.449759901950437</v>
       </c>
       <c r="G3">
-        <v>-19.01491646936864</v>
+        <v>-19.37195145667092</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-21.40183007381229</v>
       </c>
       <c r="E4">
-        <v>-21.25560663096312</v>
+        <v>-19.30000893370906</v>
       </c>
       <c r="F4">
-        <v>-1.333687404735365</v>
+        <v>-1.307845655237632</v>
       </c>
       <c r="G4">
-        <v>-17.38222337607346</v>
+        <v>-18.5599498417091</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-20.79150596057794</v>
       </c>
       <c r="E5">
-        <v>-22.5974386054227</v>
+        <v>-20.36785355706969</v>
       </c>
       <c r="F5">
-        <v>-0.628195880630124</v>
+        <v>-1.376868540708498</v>
       </c>
       <c r="G5">
-        <v>-16.30436833402627</v>
+        <v>-18.19714510886045</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-19.98085312150955</v>
       </c>
       <c r="E6">
-        <v>-21.48087266001049</v>
+        <v>-21.82606681927362</v>
       </c>
       <c r="F6">
-        <v>-1.169502500398295</v>
+        <v>-0.9898403795073182</v>
       </c>
       <c r="G6">
-        <v>-16.5224320813713</v>
+        <v>-18.06998748817798</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-19.0156030211207</v>
       </c>
       <c r="E7">
-        <v>-23.58283367756285</v>
+        <v>-22.83703736675206</v>
       </c>
       <c r="F7">
-        <v>-0.9867240613379864</v>
+        <v>-1.015373147963807</v>
       </c>
       <c r="G7">
-        <v>-16.51942972509152</v>
+        <v>-17.45422510115177</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.93274662919646</v>
       </c>
       <c r="E8">
-        <v>-23.1437603295133</v>
+        <v>-22.63309807785768</v>
       </c>
       <c r="F8">
-        <v>-1.01133485687516</v>
+        <v>-0.6879915816012063</v>
       </c>
       <c r="G8">
-        <v>-16.34313005897053</v>
+        <v>-16.90043395848483</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.76545925815181</v>
       </c>
       <c r="E9">
-        <v>-22.423605945422</v>
+        <v>-23.34905356529957</v>
       </c>
       <c r="F9">
-        <v>-1.463273059392306</v>
+        <v>-0.728156631860746</v>
       </c>
       <c r="G9">
-        <v>-16.29053269306567</v>
+        <v>-16.19851830532417</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.56964572031381</v>
       </c>
       <c r="E10">
-        <v>-23.2525744662238</v>
+        <v>-24.52362326007433</v>
       </c>
       <c r="F10">
-        <v>-0.7176396793148034</v>
+        <v>-0.605351992763122</v>
       </c>
       <c r="G10">
-        <v>-15.79491938286709</v>
+        <v>-15.46320992347089</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.38245138394798</v>
       </c>
       <c r="E11">
-        <v>-24.62157259595909</v>
+        <v>-23.67224401096375</v>
       </c>
       <c r="F11">
-        <v>-0.7214402289588476</v>
+        <v>-0.7316084388282115</v>
       </c>
       <c r="G11">
-        <v>-15.03217076998891</v>
+        <v>-15.26825648724639</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.27701307196878</v>
       </c>
       <c r="E12">
-        <v>-25.65764099947346</v>
+        <v>-25.22042413688611</v>
       </c>
       <c r="F12">
-        <v>-0.5254750092133741</v>
+        <v>-0.6318059057715243</v>
       </c>
       <c r="G12">
-        <v>-13.94411685419653</v>
+        <v>-14.47524542844032</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.28453095867666</v>
       </c>
       <c r="E13">
-        <v>-27.10685009952516</v>
+        <v>-25.75437759765137</v>
       </c>
       <c r="F13">
-        <v>-0.5880581664948767</v>
+        <v>-0.7839380643978618</v>
       </c>
       <c r="G13">
-        <v>-14.21432630863217</v>
+        <v>-13.71457105213978</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.45074342683667</v>
       </c>
       <c r="E14">
-        <v>-27.71060242981549</v>
+        <v>-27.54235168583536</v>
       </c>
       <c r="F14">
-        <v>-0.6952721027044112</v>
+        <v>-0.3654485092383573</v>
       </c>
       <c r="G14">
-        <v>-11.97625637029423</v>
+        <v>-13.0940127272997</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.78243440185422</v>
       </c>
       <c r="E15">
-        <v>-26.8243777376896</v>
+        <v>-28.7191599615142</v>
       </c>
       <c r="F15">
-        <v>-0.3732890067058546</v>
+        <v>-0.2572405321454634</v>
       </c>
       <c r="G15">
-        <v>-11.74738414034199</v>
+        <v>-12.06524359968233</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.27398046130079</v>
       </c>
       <c r="E16">
-        <v>-29.45218930071246</v>
+        <v>-28.4316456011303</v>
       </c>
       <c r="F16">
-        <v>0.1411983900292792</v>
+        <v>-0.2250990485494398</v>
       </c>
       <c r="G16">
-        <v>-11.75043349002441</v>
+        <v>-11.86876679398892</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.915401422670966</v>
       </c>
       <c r="E17">
-        <v>-30.65859751350336</v>
+        <v>-29.67952155239394</v>
       </c>
       <c r="F17">
-        <v>-0.4770229714562282</v>
+        <v>-0.2700470921927438</v>
       </c>
       <c r="G17">
-        <v>-12.1288543916448</v>
+        <v>-11.29993906784945</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.667830649890412</v>
       </c>
       <c r="E18">
-        <v>-31.32131506157794</v>
+        <v>-30.5219734737618</v>
       </c>
       <c r="F18">
-        <v>0.199529537432212</v>
+        <v>0.1164434585640187</v>
       </c>
       <c r="G18">
-        <v>-11.06669775682398</v>
+        <v>-10.77668319392016</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.507365150898256</v>
       </c>
       <c r="E19">
-        <v>-31.43463958578721</v>
+        <v>-31.16513977952475</v>
       </c>
       <c r="F19">
-        <v>-0.4900647878459037</v>
+        <v>0.3844807841900632</v>
       </c>
       <c r="G19">
-        <v>-10.91116917466988</v>
+        <v>-10.44177687777215</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.379732867597607</v>
       </c>
       <c r="E20">
-        <v>-31.05423865412351</v>
+        <v>-32.25227191627789</v>
       </c>
       <c r="F20">
-        <v>0.3399452675133534</v>
+        <v>0.136195879283773</v>
       </c>
       <c r="G20">
-        <v>-10.69372417379294</v>
+        <v>-10.30503782444029</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.255186238388289</v>
       </c>
       <c r="E21">
-        <v>-33.62525712888501</v>
+        <v>-32.87286967170172</v>
       </c>
       <c r="F21">
-        <v>0.07140015266939284</v>
+        <v>0.3400670375215649</v>
       </c>
       <c r="G21">
-        <v>-10.82663195943734</v>
+        <v>-9.670863161185261</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.090220310496214</v>
       </c>
       <c r="E22">
-        <v>-33.4513642473201</v>
+        <v>-32.20454736494429</v>
       </c>
       <c r="F22">
-        <v>0.04824976886335505</v>
+        <v>0.08095951249769913</v>
       </c>
       <c r="G22">
-        <v>-9.383609460686545</v>
+        <v>-10.08033103748317</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.861380951651373</v>
       </c>
       <c r="E23">
-        <v>-32.51007212623831</v>
+        <v>-33.24572006517688</v>
       </c>
       <c r="F23">
-        <v>0.6450735719671484</v>
+        <v>0.9706285882065766</v>
       </c>
       <c r="G23">
-        <v>-10.36133592080306</v>
+        <v>-9.459875837054442</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.559686561079122</v>
       </c>
       <c r="E24">
-        <v>-34.44423302323928</v>
+        <v>-33.07077226793546</v>
       </c>
       <c r="F24">
-        <v>0.4258030637113137</v>
+        <v>0.5152120709650756</v>
       </c>
       <c r="G24">
-        <v>-9.665119523084812</v>
+        <v>-9.435007189451792</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.183919695757769</v>
       </c>
       <c r="E25">
-        <v>-35.85186640132378</v>
+        <v>-33.80493128061408</v>
       </c>
       <c r="F25">
-        <v>-0.5266405221491131</v>
+        <v>0.4532634431141173</v>
       </c>
       <c r="G25">
-        <v>-9.374457495522398</v>
+        <v>-9.592878914876412</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.762566787735873</v>
       </c>
       <c r="E26">
-        <v>-33.82657989464475</v>
+        <v>-33.17430144323513</v>
       </c>
       <c r="F26">
-        <v>-0.02073584007438498</v>
+        <v>0.4008559510086038</v>
       </c>
       <c r="G26">
-        <v>-10.73352236433988</v>
+        <v>-9.974496673248623</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.32002380895112</v>
       </c>
       <c r="E27">
-        <v>-34.05535538726161</v>
+        <v>-34.74825016882239</v>
       </c>
       <c r="F27">
-        <v>0.2110049110631935</v>
+        <v>0.2291585826955447</v>
       </c>
       <c r="G27">
-        <v>-9.249680873907025</v>
+        <v>-10.00817788921858</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.90741342627029</v>
       </c>
       <c r="E28">
-        <v>-34.81153472638446</v>
+        <v>-33.58062256677708</v>
       </c>
       <c r="F28">
-        <v>0.2327412717126525</v>
+        <v>0.379717671623966</v>
       </c>
       <c r="G28">
-        <v>-9.235484950192845</v>
+        <v>-9.733633293389399</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.563652327940214</v>
       </c>
       <c r="E29">
-        <v>-32.26914641389067</v>
+        <v>-33.14004367962228</v>
       </c>
       <c r="F29">
-        <v>0.2432433136453447</v>
+        <v>0.1997101215260222</v>
       </c>
       <c r="G29">
-        <v>-9.397418994201239</v>
+        <v>-9.213643460943592</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.333192680005358</v>
       </c>
       <c r="E30">
-        <v>-32.92619690511252</v>
+        <v>-33.10630714403069</v>
       </c>
       <c r="F30">
-        <v>0.183663816566393</v>
+        <v>0.5164355696190104</v>
       </c>
       <c r="G30">
-        <v>-9.798916267262483</v>
+        <v>-9.986493044644789</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.247597647257286</v>
       </c>
       <c r="E31">
-        <v>-33.4301039585483</v>
+        <v>-32.62564769098564</v>
       </c>
       <c r="F31">
-        <v>-0.4122943426014749</v>
+        <v>0.5353256598724504</v>
       </c>
       <c r="G31">
-        <v>-9.63438192164134</v>
+        <v>-9.665426285574268</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.315337109326888</v>
       </c>
       <c r="E32">
-        <v>-32.52093277385273</v>
+        <v>-32.50204604535308</v>
       </c>
       <c r="F32">
-        <v>-0.309556903836669</v>
+        <v>0.3407197910349709</v>
       </c>
       <c r="G32">
-        <v>-10.05959911468514</v>
+        <v>-9.989216051253321</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.543638754811986</v>
       </c>
       <c r="E33">
-        <v>-32.82318065141147</v>
+        <v>-32.00531989429793</v>
       </c>
       <c r="F33">
-        <v>-0.2176478837612583</v>
+        <v>0.1159406395505194</v>
       </c>
       <c r="G33">
-        <v>-10.49956440392415</v>
+        <v>-10.78341499884835</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.904068171450716</v>
       </c>
       <c r="E34">
-        <v>-32.08469814574371</v>
+        <v>-32.02315793693806</v>
       </c>
       <c r="F34">
-        <v>-0.3564706633268162</v>
+        <v>0.514140163545853</v>
       </c>
       <c r="G34">
-        <v>-9.670677798319293</v>
+        <v>-9.976769326415187</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.374151483383932</v>
       </c>
       <c r="E35">
-        <v>-33.19122370277814</v>
+        <v>-31.8030792688354</v>
       </c>
       <c r="F35">
-        <v>0.3020805935313879</v>
+        <v>0.06047730009607855</v>
       </c>
       <c r="G35">
-        <v>-9.029464567646619</v>
+        <v>-10.59077337695928</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.906147356427891</v>
       </c>
       <c r="E36">
-        <v>-32.12982901660496</v>
+        <v>-31.56218885878402</v>
       </c>
       <c r="F36">
-        <v>0.2248353332203341</v>
+        <v>0.4244312872922777</v>
       </c>
       <c r="G36">
-        <v>-10.16460587288431</v>
+        <v>-10.43462735370938</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.464945481461415</v>
       </c>
       <c r="E37">
-        <v>-32.16233827825005</v>
+        <v>-31.11564180695544</v>
       </c>
       <c r="F37">
-        <v>0.3920081587793023</v>
+        <v>0.6989447892734088</v>
       </c>
       <c r="G37">
-        <v>-10.73738757170702</v>
+        <v>-10.46184175532715</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.012097489054081</v>
       </c>
       <c r="E38">
-        <v>-29.72565957700146</v>
+        <v>-29.93651188614602</v>
       </c>
       <c r="F38">
-        <v>0.2724076447957069</v>
+        <v>0.5410645892390453</v>
       </c>
       <c r="G38">
-        <v>-9.955577912569121</v>
+        <v>-10.62059591242357</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.51277859953332</v>
       </c>
       <c r="E39">
-        <v>-30.80491099526574</v>
+        <v>-30.00388320365172</v>
       </c>
       <c r="F39">
-        <v>0.2305055080924967</v>
+        <v>0.5510439313405709</v>
       </c>
       <c r="G39">
-        <v>-10.66453866000889</v>
+        <v>-11.21958687619646</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.951789178967831</v>
       </c>
       <c r="E40">
-        <v>-29.4004569004504</v>
+        <v>-28.90855885756035</v>
       </c>
       <c r="F40">
-        <v>0.2052982880253077</v>
+        <v>0.6956130955793491</v>
       </c>
       <c r="G40">
-        <v>-12.41246871418351</v>
+        <v>-11.43763626444624</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.30827268084935</v>
       </c>
       <c r="E41">
-        <v>-29.53990304728718</v>
+        <v>-29.08608787564015</v>
       </c>
       <c r="F41">
-        <v>0.9630722207582395</v>
+        <v>1.350305817075313</v>
       </c>
       <c r="G41">
-        <v>-11.09724738465689</v>
+        <v>-11.07507955233375</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.58716904007917</v>
       </c>
       <c r="E42">
-        <v>-29.1724850542249</v>
+        <v>-28.39131376595488</v>
       </c>
       <c r="F42">
-        <v>0.1300071464174579</v>
+        <v>0.8254986192361031</v>
       </c>
       <c r="G42">
-        <v>-12.24114251650859</v>
+        <v>-11.53492566163408</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.78318377442804</v>
       </c>
       <c r="E43">
-        <v>-29.34943469932488</v>
+        <v>-27.46825839580042</v>
       </c>
       <c r="F43">
-        <v>0.6890060371746203</v>
+        <v>0.9962847834060828</v>
       </c>
       <c r="G43">
-        <v>-11.45284124094489</v>
+        <v>-11.60411039329858</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.91033271665302</v>
       </c>
       <c r="E44">
-        <v>-27.21746257673932</v>
+        <v>-27.77541744575076</v>
       </c>
       <c r="F44">
-        <v>0.4408089392130268</v>
+        <v>1.186950108508445</v>
       </c>
       <c r="G44">
-        <v>-11.33675448270103</v>
+        <v>-12.38201698927277</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.97689994451825</v>
       </c>
       <c r="E45">
-        <v>-28.45084174387365</v>
+        <v>-26.39349452237261</v>
       </c>
       <c r="F45">
-        <v>1.067035643279189</v>
+        <v>0.9666226034466382</v>
       </c>
       <c r="G45">
-        <v>-11.81164892382454</v>
+        <v>-12.55629593908024</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.99674632265228</v>
       </c>
       <c r="E46">
-        <v>-27.50443286643967</v>
+        <v>-26.0521005514717</v>
       </c>
       <c r="F46">
-        <v>1.06163303107813</v>
+        <v>1.218787581267641</v>
       </c>
       <c r="G46">
-        <v>-12.38035002885134</v>
+        <v>-12.31520672981388</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.99124187155798</v>
       </c>
       <c r="E47">
-        <v>-27.6806619293748</v>
+        <v>-25.51818031639705</v>
       </c>
       <c r="F47">
-        <v>1.009288494895229</v>
+        <v>1.526620505291577</v>
       </c>
       <c r="G47">
-        <v>-11.97939317992046</v>
+        <v>-12.75324398417234</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.9691561744613</v>
       </c>
       <c r="E48">
-        <v>-26.68708503092474</v>
+        <v>-25.22549105470241</v>
       </c>
       <c r="F48">
-        <v>0.7477745625662312</v>
+        <v>1.241286039927676</v>
       </c>
       <c r="G48">
-        <v>-13.21504554117142</v>
+        <v>-12.76047705206202</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.9590410836234</v>
       </c>
       <c r="E49">
-        <v>-27.25646953750211</v>
+        <v>-24.08537640107842</v>
       </c>
       <c r="F49">
-        <v>1.56956804165712</v>
+        <v>1.121550502057424</v>
       </c>
       <c r="G49">
-        <v>-12.54919210304782</v>
+        <v>-13.34235066892328</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.96618501359879</v>
       </c>
       <c r="E50">
-        <v>-25.88074735863193</v>
+        <v>-23.67856104538882</v>
       </c>
       <c r="F50">
-        <v>1.297951340483579</v>
+        <v>1.451416342261021</v>
       </c>
       <c r="G50">
-        <v>-11.85762413607405</v>
+        <v>-13.35064500448925</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.01454488987958</v>
       </c>
       <c r="E51">
-        <v>-24.23642454375111</v>
+        <v>-23.73521915428213</v>
       </c>
       <c r="F51">
-        <v>1.414472812830968</v>
+        <v>1.211887280802321</v>
       </c>
       <c r="G51">
-        <v>-12.51283356849968</v>
+        <v>-13.06677613435291</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.1051611143069</v>
       </c>
       <c r="E52">
-        <v>-24.77060227792791</v>
+        <v>-23.35158287099639</v>
       </c>
       <c r="F52">
-        <v>0.6739446610569196</v>
+        <v>1.183681370736998</v>
       </c>
       <c r="G52">
-        <v>-12.88894135041235</v>
+        <v>-13.90756381917635</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.24770735214397</v>
       </c>
       <c r="E53">
-        <v>-23.79003323734722</v>
+        <v>-22.22883279392152</v>
       </c>
       <c r="F53">
-        <v>0.7484919287370555</v>
+        <v>1.112100486726287</v>
       </c>
       <c r="G53">
-        <v>-13.46416931691693</v>
+        <v>-13.91151257037041</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.44157638556289</v>
       </c>
       <c r="E54">
-        <v>-22.61633987016199</v>
+        <v>-21.7564091589336</v>
       </c>
       <c r="F54">
-        <v>1.025708393553521</v>
+        <v>1.135945870783274</v>
       </c>
       <c r="G54">
-        <v>-14.33804688406043</v>
+        <v>-13.87735358814029</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.67193900118923</v>
       </c>
       <c r="E55">
-        <v>-23.09818298843463</v>
+        <v>-20.71647826888713</v>
       </c>
       <c r="F55">
-        <v>0.9054344168714499</v>
+        <v>1.193981291023407</v>
       </c>
       <c r="G55">
-        <v>-13.67914194266608</v>
+        <v>-14.58852172013184</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.93963913484671</v>
       </c>
       <c r="E56">
-        <v>-23.23720343111061</v>
+        <v>-21.26039528362065</v>
       </c>
       <c r="F56">
-        <v>0.7214540167096797</v>
+        <v>1.14088625397357</v>
       </c>
       <c r="G56">
-        <v>-13.23788041873759</v>
+        <v>-14.33690859941871</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.22012315603016</v>
       </c>
       <c r="E57">
-        <v>-23.2040981836404</v>
+        <v>-20.27111280568046</v>
       </c>
       <c r="F57">
-        <v>0.4627349959977269</v>
+        <v>0.9174573413556819</v>
       </c>
       <c r="G57">
-        <v>-12.90010097816706</v>
+        <v>-14.49005618250571</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.51419996076996</v>
       </c>
       <c r="E58">
-        <v>-22.66377369670286</v>
+        <v>-19.81133985238797</v>
       </c>
       <c r="F58">
-        <v>0.5490624765130746</v>
+        <v>1.211940296316101</v>
       </c>
       <c r="G58">
-        <v>-13.84461615634002</v>
+        <v>-14.12324917819888</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.79999723481668</v>
       </c>
       <c r="E59">
-        <v>-20.63305686621662</v>
+        <v>-19.09339082351016</v>
       </c>
       <c r="F59">
-        <v>1.682578892951445</v>
+        <v>1.206552594728292</v>
       </c>
       <c r="G59">
-        <v>-14.99984191971715</v>
+        <v>-14.59270804908369</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-13.07698216816488</v>
       </c>
       <c r="E60">
-        <v>-21.22838233072887</v>
+        <v>-19.15303093813469</v>
       </c>
       <c r="F60">
-        <v>1.44595077413735</v>
+        <v>1.216347210898994</v>
       </c>
       <c r="G60">
-        <v>-14.75374008083586</v>
+        <v>-15.19686176028551</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.33433814837518</v>
       </c>
       <c r="E61">
-        <v>-21.32363207925249</v>
+        <v>-18.52055499832186</v>
       </c>
       <c r="F61">
-        <v>0.3710653741017252</v>
+        <v>1.169730006939049</v>
       </c>
       <c r="G61">
-        <v>-14.06074664731534</v>
+        <v>-14.87759772035516</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.56313262394089</v>
       </c>
       <c r="E62">
-        <v>-20.67433978678542</v>
+        <v>-18.99207738645229</v>
       </c>
       <c r="F62">
-        <v>0.974902964005022</v>
+        <v>0.8143471372596163</v>
       </c>
       <c r="G62">
-        <v>-14.12163312729698</v>
+        <v>-14.60678910003586</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.76565981441721</v>
       </c>
       <c r="E63">
-        <v>-21.30897539648717</v>
+        <v>-18.3081223922682</v>
       </c>
       <c r="F63">
-        <v>0.7175954813474396</v>
+        <v>0.7686328537687227</v>
       </c>
       <c r="G63">
-        <v>-13.92429999737769</v>
+        <v>-15.48166397161317</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.92658584772648</v>
       </c>
       <c r="E64">
-        <v>-19.2789895311941</v>
+        <v>-18.26041030056857</v>
       </c>
       <c r="F64">
-        <v>0.7520704759171494</v>
+        <v>0.9390098044417194</v>
       </c>
       <c r="G64">
-        <v>-14.30449228920315</v>
+        <v>-14.93988747555453</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.0552364787687</v>
       </c>
       <c r="E65">
-        <v>-19.09941713314248</v>
+        <v>-17.09043405751907</v>
       </c>
       <c r="F65">
-        <v>0.929380861751578</v>
+        <v>1.080602644602239</v>
       </c>
       <c r="G65">
-        <v>-14.68596906736744</v>
+        <v>-15.19993069055237</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-14.13762525020991</v>
       </c>
       <c r="E66">
-        <v>-20.96884815504033</v>
+        <v>-17.18992838801666</v>
       </c>
       <c r="F66">
-        <v>0.1209481205004425</v>
+        <v>0.7231074380456675</v>
       </c>
       <c r="G66">
-        <v>-14.07706771712668</v>
+        <v>-15.31199429138131</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.18482202312557</v>
       </c>
       <c r="E67">
-        <v>-20.04122009921723</v>
+        <v>-17.44589495517717</v>
       </c>
       <c r="F67">
-        <v>0.6825389728609645</v>
+        <v>0.5873943497102189</v>
       </c>
       <c r="G67">
-        <v>-15.77514168721711</v>
+        <v>-15.2568266474265</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-14.19004666716646</v>
       </c>
       <c r="E68">
-        <v>-18.68716937704</v>
+        <v>-17.59254484705687</v>
       </c>
       <c r="F68">
-        <v>0.1718405286262357</v>
+        <v>0.2513737397038218</v>
       </c>
       <c r="G68">
-        <v>-14.24269335398691</v>
+        <v>-15.27786663808628</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-14.15857698616132</v>
       </c>
       <c r="E69">
-        <v>-18.49705197543465</v>
+        <v>-17.29912046695773</v>
       </c>
       <c r="F69">
-        <v>0.6120507054545462</v>
+        <v>0.6560767761785343</v>
       </c>
       <c r="G69">
-        <v>-14.60511430738066</v>
+        <v>-15.26395398016024</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-14.09551249422796</v>
       </c>
       <c r="E70">
-        <v>-19.33049765804462</v>
+        <v>-16.88859629355505</v>
       </c>
       <c r="F70">
-        <v>0.2399803744457174</v>
+        <v>0.6486438354732144</v>
       </c>
       <c r="G70">
-        <v>-13.72181064689094</v>
+        <v>-15.01078877178769</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.9956072240777</v>
       </c>
       <c r="E71">
-        <v>-18.7714754137227</v>
+        <v>-17.34086854719491</v>
       </c>
       <c r="F71">
-        <v>0.4265013774318737</v>
+        <v>0.5563338855748486</v>
       </c>
       <c r="G71">
-        <v>-14.46656339730258</v>
+        <v>-15.18505988936139</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.87470213716189</v>
       </c>
       <c r="E72">
-        <v>-19.37896148099404</v>
+        <v>-17.60538242326191</v>
       </c>
       <c r="F72">
-        <v>0.4903858999031744</v>
+        <v>0.2797121885535929</v>
       </c>
       <c r="G72">
-        <v>-14.66523453382482</v>
+        <v>-14.89796674965502</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-13.72466238476793</v>
       </c>
       <c r="E73">
-        <v>-18.66535255795068</v>
+        <v>-18.36368405337176</v>
       </c>
       <c r="F73">
-        <v>0.3227541588030552</v>
+        <v>0.4090849527880141</v>
       </c>
       <c r="G73">
-        <v>-13.81274027025482</v>
+        <v>-14.4822161164986</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-13.56240724841331</v>
       </c>
       <c r="E74">
-        <v>-19.41893613999552</v>
+        <v>-18.09039028856407</v>
       </c>
       <c r="F74">
-        <v>0.3953622183932375</v>
+        <v>0.4991723929446688</v>
       </c>
       <c r="G74">
-        <v>-13.48158428871195</v>
+        <v>-14.63694058931863</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-13.3786263664057</v>
       </c>
       <c r="E75">
-        <v>-22.1722577492547</v>
+        <v>-18.08407740735032</v>
       </c>
       <c r="F75">
-        <v>0.4515445807533083</v>
+        <v>0.4505770476268385</v>
       </c>
       <c r="G75">
-        <v>-13.38758051359203</v>
+        <v>-14.4057147731175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-13.1847944097402</v>
       </c>
       <c r="E76">
-        <v>-20.06007152542062</v>
+        <v>-18.04943131847861</v>
       </c>
       <c r="F76">
-        <v>-0.197651923025081</v>
+        <v>0.2487478150369474</v>
       </c>
       <c r="G76">
-        <v>-14.68285967055943</v>
+        <v>-14.41619952339541</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.98202758969417</v>
       </c>
       <c r="E77">
-        <v>-20.52031794480415</v>
+        <v>-18.22333458307183</v>
       </c>
       <c r="F77">
-        <v>0.1657942749532021</v>
+        <v>0.4466853775684865</v>
       </c>
       <c r="G77">
-        <v>-13.60293300267919</v>
+        <v>-14.49734015991491</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.77195337051406</v>
       </c>
       <c r="E78">
-        <v>-22.24738934212085</v>
+        <v>-19.24089627692277</v>
       </c>
       <c r="F78">
-        <v>0.5511118574676005</v>
+        <v>0.2359280011112223</v>
       </c>
       <c r="G78">
-        <v>-14.56892677660324</v>
+        <v>-13.5369464331388</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.56758209182045</v>
       </c>
       <c r="E79">
-        <v>-21.2350108560033</v>
+        <v>-19.55646142659457</v>
       </c>
       <c r="F79">
-        <v>0.09341981497060929</v>
+        <v>0.3389363160167436</v>
       </c>
       <c r="G79">
-        <v>-12.70792015269832</v>
+        <v>-13.06620829740435</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.36145977967832</v>
       </c>
       <c r="E80">
-        <v>-22.23738840925066</v>
+        <v>-19.42262419165197</v>
       </c>
       <c r="F80">
-        <v>-0.3710333622680315</v>
+        <v>0.2001955448240628</v>
       </c>
       <c r="G80">
-        <v>-13.04056556403043</v>
+        <v>-13.38441890189219</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.16862190206879</v>
       </c>
       <c r="E81">
-        <v>-23.91842145903164</v>
+        <v>-20.27843076403481</v>
       </c>
       <c r="F81">
-        <v>0.4633446744061873</v>
+        <v>0.1795857638424111</v>
       </c>
       <c r="G81">
-        <v>-11.95671494702975</v>
+        <v>-12.65568698566392</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.97861522358985</v>
       </c>
       <c r="E82">
-        <v>-23.72058739078476</v>
+        <v>-20.64873108575652</v>
       </c>
       <c r="F82">
-        <v>0.1435236173289374</v>
+        <v>0.1420516084541627</v>
       </c>
       <c r="G82">
-        <v>-12.92859595000676</v>
+        <v>-13.19931449963767</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.80380236103222</v>
       </c>
       <c r="E83">
-        <v>-21.86023944205431</v>
+        <v>-21.77811384131715</v>
       </c>
       <c r="F83">
-        <v>-0.2834815547313462</v>
+        <v>0.2338537691346123</v>
       </c>
       <c r="G83">
-        <v>-13.61904129680636</v>
+        <v>-12.62259579797156</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.63876473618854</v>
       </c>
       <c r="E84">
-        <v>-24.45338415014883</v>
+        <v>-22.41036966092977</v>
       </c>
       <c r="F84">
-        <v>0.7353258572369602</v>
+        <v>0.1519911889203539</v>
       </c>
       <c r="G84">
-        <v>-12.50593467591766</v>
+        <v>-12.57371743773674</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-11.48618694314062</v>
       </c>
       <c r="E85">
-        <v>-25.52803588687086</v>
+        <v>-23.99209527472278</v>
       </c>
       <c r="F85">
-        <v>0.4854256358952109</v>
+        <v>0.2476676239436968</v>
       </c>
       <c r="G85">
-        <v>-13.0357265489308</v>
+        <v>-11.70994867365002</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-11.3525351303202</v>
       </c>
       <c r="E86">
-        <v>-26.85671048785339</v>
+        <v>-25.19660546993822</v>
       </c>
       <c r="F86">
-        <v>-0.07494834475059862</v>
+        <v>0.218563763613739</v>
       </c>
       <c r="G86">
-        <v>-12.14828746900876</v>
+        <v>-11.97608145040663</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-11.23143755762199</v>
       </c>
       <c r="E87">
-        <v>-26.08942961485926</v>
+        <v>-25.74406932714315</v>
       </c>
       <c r="F87">
-        <v>-0.7235426254271528</v>
+        <v>0.1114392910837069</v>
       </c>
       <c r="G87">
-        <v>-11.89678399956845</v>
+        <v>-12.02140658725295</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-11.13793447628997</v>
       </c>
       <c r="E88">
-        <v>-30.1756288749617</v>
+        <v>-27.34577188740857</v>
       </c>
       <c r="F88">
-        <v>0.24096944512466</v>
+        <v>0.09529275366833898</v>
       </c>
       <c r="G88">
-        <v>-11.34912810669062</v>
+        <v>-11.90045862258044</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-11.06401107370752</v>
       </c>
       <c r="E89">
-        <v>-29.44078665902014</v>
+        <v>-27.43607931445564</v>
       </c>
       <c r="F89">
-        <v>0.7652829359918015</v>
+        <v>-0.1299519402964858</v>
       </c>
       <c r="G89">
-        <v>-11.28570006684952</v>
+        <v>-11.88197977236454</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-11.02659421698992</v>
       </c>
       <c r="E90">
-        <v>-31.21593978384439</v>
+        <v>-29.35003276175566</v>
       </c>
       <c r="F90">
-        <v>0.2000936556335184</v>
+        <v>-0.03674486850088822</v>
       </c>
       <c r="G90">
-        <v>-10.53319732111916</v>
+        <v>-11.48877291875238</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-11.02162788308596</v>
       </c>
       <c r="E91">
-        <v>-32.9921332881055</v>
+        <v>-31.02925708800467</v>
       </c>
       <c r="F91">
-        <v>0.1378012553103984</v>
+        <v>-0.2021888912902139</v>
       </c>
       <c r="G91">
-        <v>-11.2572090111267</v>
+        <v>-11.68268205714043</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-11.0596040195182</v>
       </c>
       <c r="E92">
-        <v>-33.6734738357606</v>
+        <v>-32.65989507157018</v>
       </c>
       <c r="F92">
-        <v>-0.4782555821515939</v>
+        <v>-0.04628766098113853</v>
       </c>
       <c r="G92">
-        <v>-11.63735692029411</v>
+        <v>-11.6214966469031</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-11.14456936644659</v>
       </c>
       <c r="E93">
-        <v>-34.97894236846565</v>
+        <v>-34.27176053994746</v>
       </c>
       <c r="F93">
-        <v>0.03161615141514098</v>
+        <v>-0.1832259047053276</v>
       </c>
       <c r="G93">
-        <v>-11.25889816287715</v>
+        <v>-11.41086307866438</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-11.26813714803713</v>
       </c>
       <c r="E94">
-        <v>-37.85091291885254</v>
+        <v>-36.48587279950981</v>
       </c>
       <c r="F94">
-        <v>0.2882609401504838</v>
+        <v>-0.05099527293124811</v>
       </c>
       <c r="G94">
-        <v>-10.9494740193107</v>
+        <v>-11.5663825232124</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-11.43509573006165</v>
       </c>
       <c r="E95">
-        <v>-37.73565922798288</v>
+        <v>-37.59698557845252</v>
       </c>
       <c r="F95">
-        <v>-0.06377946705865288</v>
+        <v>-0.6096595032576795</v>
       </c>
       <c r="G95">
-        <v>-11.42086484119293</v>
+        <v>-12.30209557047731</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.6238831674539</v>
       </c>
       <c r="E96">
-        <v>-41.40854958648934</v>
+        <v>-40.47379254342717</v>
       </c>
       <c r="F96">
-        <v>-0.6647906673835978</v>
+        <v>-0.4172280988525487</v>
       </c>
       <c r="G96">
-        <v>-10.87286955151825</v>
+        <v>-12.29197240832527</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.83100567033589</v>
       </c>
       <c r="E97">
-        <v>-43.15995257235255</v>
+        <v>-41.70200719227908</v>
       </c>
       <c r="F97">
-        <v>-0.858451369014483</v>
+        <v>-0.6745687162062431</v>
       </c>
       <c r="G97">
-        <v>-11.99585653531202</v>
+        <v>-12.16282801100896</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.03274544383757</v>
       </c>
       <c r="E98">
-        <v>-45.57578007614484</v>
+        <v>-44.85181512066301</v>
       </c>
       <c r="F98">
-        <v>-0.9363005091621778</v>
+        <v>-0.4892977196309113</v>
       </c>
       <c r="G98">
-        <v>-11.7077791448948</v>
+        <v>-12.12665614469909</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.21743714388089</v>
       </c>
       <c r="E99">
-        <v>-46.10507259550081</v>
+        <v>-46.64949422541029</v>
       </c>
       <c r="F99">
-        <v>-0.4616045689879211</v>
+        <v>-0.6642050116298185</v>
       </c>
       <c r="G99">
-        <v>-11.86802012103586</v>
+        <v>-12.6654759725083</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.37510537683547</v>
       </c>
       <c r="E100">
-        <v>-48.62299122517154</v>
+        <v>-48.52265067786652</v>
       </c>
       <c r="F100">
-        <v>-0.372915413007192</v>
+        <v>-0.8663192026062727</v>
       </c>
       <c r="G100">
-        <v>-11.877644630971</v>
+        <v>-12.84863798078703</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.48330718716512</v>
       </c>
       <c r="E101">
-        <v>-49.8452719733431</v>
+        <v>-49.78426337558703</v>
       </c>
       <c r="F101">
-        <v>-1.254947769629661</v>
+        <v>-0.5202554662083344</v>
       </c>
       <c r="G101">
-        <v>-12.61998635875274</v>
+        <v>-12.80160411160583</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.56227894714004</v>
       </c>
       <c r="E102">
-        <v>-52.09209596360264</v>
+        <v>-52.71391683976163</v>
       </c>
       <c r="F102">
-        <v>-1.231268887420637</v>
+        <v>-0.924177352222207</v>
       </c>
       <c r="G102">
-        <v>-13.27187361868618</v>
+        <v>-13.45600551858051</v>
       </c>
     </row>
   </sheetData>
